--- a/data/trans_orig/P22_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P22_R-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el Seguro Sanitario del que es beneficiario en 2007</t>
+          <t>Población según el Seguro Sanitario del que es beneficiaria en 2007 (tasa de respuesta: 99,88%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1037</t>
+          <t>1036</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10786</t>
+          <t>13000</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5457</t>
+          <t>5601</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1651</t>
+          <t>1652</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>13049</t>
+          <t>12910</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,55%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>27480</t>
+          <t>27740</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>52743</t>
+          <t>53386</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>18701</t>
+          <t>18707</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>38940</t>
+          <t>39476</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>50011</t>
+          <t>49869</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>83312</t>
+          <t>81411</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,47%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>9206</t>
+          <t>9447</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>24897</t>
+          <t>25029</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>26916</t>
+          <t>27243</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>51033</t>
+          <t>51138</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>39595</t>
+          <t>39833</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>70455</t>
+          <t>68815</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,94%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>952790</t>
+          <t>953307</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>984518</t>
+          <t>983447</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>92,6%</t>
+          <t>92,65%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>95,69%</t>
+          <t>95,58%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1229877</t>
+          <t>1230978</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1262863</t>
+          <t>1262334</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>93,58%</t>
+          <t>93,66%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>96,05%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2195166</t>
+          <t>2196378</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>2240702</t>
+          <t>2239163</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>93,68%</t>
+          <t>93,74%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>95,63%</t>
+          <t>95,56%</t>
         </is>
       </c>
     </row>
@@ -1307,7 +1307,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8805</t>
+          <t>8865</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4740</t>
+          <t>6957</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1357,42 +1357,42 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
+          <t>0,44%</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>2822</t>
+        </is>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>9849</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
+          <t>0,09%</t>
+        </is>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="W9" s="2" t="inlineStr">
+        <is>
           <t>0,3%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>2822</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>9169</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>0,09%</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="W9" s="2" t="inlineStr">
-        <is>
-          <t>0,28%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>81838</t>
+          <t>83082</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>123026</t>
+          <t>124120</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>68828</t>
+          <t>67111</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>103832</t>
+          <t>102914</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>161165</t>
+          <t>160301</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>217760</t>
+          <t>214492</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,55%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>35043</t>
+          <t>35256</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>62603</t>
+          <t>63939</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>46803</t>
+          <t>45638</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>77136</t>
+          <t>77749</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>90200</t>
+          <t>89693</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>132500</t>
+          <t>130819</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>3,99%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1512578</t>
+          <t>1511181</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1560363</t>
+          <t>1561041</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>89,51%</t>
+          <t>89,43%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>92,34%</t>
+          <t>92,38%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1417262</t>
+          <t>1413250</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1463106</t>
+          <t>1461658</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>89,33%</t>
+          <t>89,08%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>92,22%</t>
+          <t>92,13%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>2936694</t>
+          <t>2943526</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>3006924</t>
+          <t>3010339</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>89,63%</t>
+          <t>89,84%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>91,78%</t>
+          <t>91,88%</t>
         </is>
       </c>
     </row>
@@ -1871,97 +1871,97 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>2005</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>0,36%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
+      <c r="R14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>0,42%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>2014</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1984,12 +1984,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>60786</t>
+          <t>59394</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>93344</t>
+          <t>92359</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1999,12 +1999,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>16,75%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2019,12 +2019,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>51214</t>
+          <t>50717</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>81231</t>
+          <t>81344</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2034,12 +2034,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>17,07%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2054,12 +2054,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>117267</t>
+          <t>118718</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>162842</t>
+          <t>161625</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2069,12 +2069,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>15,84%</t>
+          <t>15,73%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>53060</t>
+          <t>51773</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>85131</t>
+          <t>82790</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>15,01%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>35077</t>
+          <t>36149</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>60475</t>
+          <t>62606</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>13,14%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>94095</t>
+          <t>95152</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>134115</t>
+          <t>137153</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>13,05%</t>
+          <t>13,34%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>389060</t>
+          <t>389801</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>430130</t>
+          <t>432953</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>70,56%</t>
+          <t>70,69%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>78,01%</t>
+          <t>78,52%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>342551</t>
+          <t>342290</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>380999</t>
+          <t>382538</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>71,9%</t>
+          <t>71,85%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>79,97%</t>
+          <t>80,3%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>748912</t>
+          <t>746141</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>802201</t>
+          <t>803096</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>72,86%</t>
+          <t>72,59%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>78,05%</t>
+          <t>78,14%</t>
         </is>
       </c>
     </row>
@@ -2440,12 +2440,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1652</t>
+          <t>1659</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>14932</t>
+          <t>15454</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2460,7 +2460,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2480,7 +2480,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>7585</t>
+          <t>6450</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2495,7 +2495,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,12 +2510,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3377</t>
+          <t>3139</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>17536</t>
+          <t>16800</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2530,7 +2530,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,25%</t>
         </is>
       </c>
     </row>
@@ -2553,12 +2553,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>190297</t>
+          <t>187060</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>244673</t>
+          <t>246072</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2568,12 +2568,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,12 +2588,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>150341</t>
+          <t>152130</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>203698</t>
+          <t>204233</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,12 +2623,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>356281</t>
+          <t>351145</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>434063</t>
+          <t>431657</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,12 +2638,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,49%</t>
         </is>
       </c>
     </row>
@@ -2666,12 +2666,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>109568</t>
+          <t>109849</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>154560</t>
+          <t>154994</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2681,82 +2681,82 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
+          <t>4,74%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>146110</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>123197</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>170664</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>4,33%</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>3,65%</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>5,05%</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr">
+        <is>
+          <t>268</t>
+        </is>
+      </c>
+      <c r="R21" s="2" t="inlineStr">
+        <is>
+          <t>276878</t>
+        </is>
+      </c>
+      <c r="S21" s="2" t="inlineStr">
+        <is>
+          <t>246468</t>
+        </is>
+      </c>
+      <c r="T21" s="2" t="inlineStr">
+        <is>
+          <t>314462</t>
+        </is>
+      </c>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>4,17%</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>3,71%</t>
+        </is>
+      </c>
+      <c r="W21" s="2" t="inlineStr">
+        <is>
           <t>4,73%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>139</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>146110</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>123093</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>169825</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>4,33%</t>
-        </is>
-      </c>
-      <c r="O21" s="2" t="inlineStr">
-        <is>
-          <t>3,64%</t>
-        </is>
-      </c>
-      <c r="P21" s="2" t="inlineStr">
-        <is>
-          <t>5,03%</t>
-        </is>
-      </c>
-      <c r="Q21" s="2" t="inlineStr">
-        <is>
-          <t>268</t>
-        </is>
-      </c>
-      <c r="R21" s="2" t="inlineStr">
-        <is>
-          <t>276878</t>
-        </is>
-      </c>
-      <c r="S21" s="2" t="inlineStr">
-        <is>
-          <t>245164</t>
-        </is>
-      </c>
-      <c r="T21" s="2" t="inlineStr">
-        <is>
-          <t>311616</t>
-        </is>
-      </c>
-      <c r="U21" s="2" t="inlineStr">
-        <is>
-          <t>4,17%</t>
-        </is>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>3,69%</t>
-        </is>
-      </c>
-      <c r="W21" s="2" t="inlineStr">
-        <is>
-          <t>4,69%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2880886</t>
+          <t>2883107</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2950648</t>
+          <t>2952586</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>88,1%</t>
+          <t>88,16%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>90,23%</t>
+          <t>90,29%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3017647</t>
+          <t>3017994</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3084749</t>
+          <t>3085285</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>89,35%</t>
+          <t>89,36%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>91,34%</t>
+          <t>91,36%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>5919098</t>
+          <t>5922062</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>6018233</t>
+          <t>6023059</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>89,05%</t>
+          <t>89,09%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>90,54%</t>
+          <t>90,61%</t>
         </is>
       </c>
     </row>
@@ -3045,7 +3045,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el Seguro Sanitario del que es beneficiario en 2012</t>
+          <t>Población según el Seguro Sanitario del que es beneficiaria en 2012 (tasa de respuesta: 99,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3245,7 +3245,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8222</t>
+          <t>7591</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3260,7 +3260,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3275,62 +3275,62 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>1268</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>2059</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>10668</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,05%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>0,15%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>1268</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>6911</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,05%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,46%</t>
         </is>
       </c>
     </row>
@@ -3353,12 +3353,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3628</t>
+          <t>3710</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>14793</t>
+          <t>14402</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3368,12 +3368,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3388,12 +3388,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>14941</t>
+          <t>15432</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>36650</t>
+          <t>36095</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3423,12 +3423,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>20715</t>
+          <t>21688</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>44510</t>
+          <t>44950</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,94%</t>
         </is>
       </c>
     </row>
@@ -3466,12 +3466,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7077</t>
+          <t>7773</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>22688</t>
+          <t>24402</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3501,12 +3501,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>12186</t>
+          <t>12078</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>31845</t>
+          <t>31467</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3536,12 +3536,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>24373</t>
+          <t>23132</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>48874</t>
+          <t>47128</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,04%</t>
         </is>
       </c>
     </row>
@@ -3579,12 +3579,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>940667</t>
+          <t>939562</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>959856</t>
+          <t>960477</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3594,12 +3594,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>96,51%</t>
+          <t>96,4%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3614,12 +3614,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1277125</t>
+          <t>1277955</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1305941</t>
+          <t>1305993</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3629,7 +3629,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,53%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -3649,12 +3649,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2227087</t>
+          <t>2230037</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>2260066</t>
+          <t>2262121</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3664,12 +3664,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>96,31%</t>
+          <t>96,44%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,82%</t>
         </is>
       </c>
     </row>
@@ -3814,7 +3814,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7401</t>
+          <t>5255</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3829,7 +3829,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3849,7 +3849,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>7217</t>
+          <t>7182</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3884,7 +3884,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>8478</t>
+          <t>9692</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3899,7 +3899,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,26%</t>
         </is>
       </c>
     </row>
@@ -3922,12 +3922,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>79849</t>
+          <t>80650</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>121731</t>
+          <t>121228</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3937,12 +3937,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3957,12 +3957,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>57526</t>
+          <t>58537</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>93302</t>
+          <t>93799</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3972,12 +3972,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3992,12 +3992,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>147595</t>
+          <t>146803</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>203073</t>
+          <t>199067</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4007,12 +4007,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,35%</t>
         </is>
       </c>
     </row>
@@ -4035,12 +4035,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>63453</t>
+          <t>61004</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>102030</t>
+          <t>100564</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4050,12 +4050,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>43990</t>
+          <t>43471</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>78278</t>
+          <t>77231</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4085,12 +4085,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>114481</t>
+          <t>115281</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>168725</t>
+          <t>168369</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4120,7 +4120,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -4148,12 +4148,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1752271</t>
+          <t>1754882</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1810775</t>
+          <t>1809878</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4163,12 +4163,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>89,27%</t>
+          <t>89,4%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>92,25%</t>
+          <t>92,2%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1600252</t>
+          <t>1597706</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1647756</t>
+          <t>1646903</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4198,12 +4198,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>91,04%</t>
+          <t>90,89%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>93,74%</t>
+          <t>93,69%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>3366330</t>
+          <t>3367619</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>3441708</t>
+          <t>3444697</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4233,12 +4233,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>90,47%</t>
+          <t>90,51%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>92,5%</t>
+          <t>92,58%</t>
         </is>
       </c>
     </row>
@@ -4383,7 +4383,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6127</t>
+          <t>6936</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4398,7 +4398,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4413,62 +4413,62 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>1211</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>2132</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>6027</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>0,13%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>0,46%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>1211</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>6554</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>0,13%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,64%</t>
         </is>
       </c>
     </row>
@@ -4491,12 +4491,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>36457</t>
+          <t>36008</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>64478</t>
+          <t>66005</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>13,72%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>37875</t>
+          <t>39271</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>66821</t>
+          <t>68570</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4541,12 +4541,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>14,95%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>82830</t>
+          <t>83416</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>123772</t>
+          <t>123926</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -4576,12 +4576,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>13,19%</t>
         </is>
       </c>
     </row>
@@ -4604,12 +4604,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>48476</t>
+          <t>50331</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>83541</t>
+          <t>84502</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4619,12 +4619,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>17,56%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4639,12 +4639,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>31270</t>
+          <t>30979</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>59008</t>
+          <t>58950</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4654,12 +4654,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4674,12 +4674,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>88010</t>
+          <t>87422</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>131949</t>
+          <t>133585</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4689,12 +4689,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>14,21%</t>
         </is>
       </c>
     </row>
@@ -4717,12 +4717,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>341625</t>
+          <t>341271</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>383896</t>
+          <t>383030</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4732,12 +4732,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>71,0%</t>
+          <t>70,92%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>79,78%</t>
+          <t>79,6%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4752,12 +4752,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>342167</t>
+          <t>344303</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>381578</t>
+          <t>382827</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4767,12 +4767,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>74,61%</t>
+          <t>75,07%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>83,2%</t>
+          <t>83,47%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4787,12 +4787,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>699204</t>
+          <t>699010</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>755251</t>
+          <t>756274</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4802,12 +4802,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>74,4%</t>
+          <t>74,38%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>80,36%</t>
+          <t>80,47%</t>
         </is>
       </c>
     </row>
@@ -4952,7 +4952,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11256</t>
+          <t>9940</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -4967,7 +4967,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -4987,7 +4987,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6073</t>
+          <t>5999</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5017,12 +5017,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1268</t>
+          <t>1266</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>12887</t>
+          <t>12300</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5060,12 +5060,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>133388</t>
+          <t>133121</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>183647</t>
+          <t>184560</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5075,12 +5075,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5095,12 +5095,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>123596</t>
+          <t>128005</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>175334</t>
+          <t>177270</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5110,47 +5110,47 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
+          <t>4,99%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>284</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>306249</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>270528</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>344047</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>4,39%</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>3,88%</t>
+        </is>
+      </c>
+      <c r="W20" s="2" t="inlineStr">
+        <is>
           <t>4,93%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>284</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>306249</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>271029</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>340650</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>4,39%</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>3,89%</t>
-        </is>
-      </c>
-      <c r="W20" s="2" t="inlineStr">
-        <is>
-          <t>4,89%</t>
         </is>
       </c>
     </row>
@@ -5173,12 +5173,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>133720</t>
+          <t>130686</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>187824</t>
+          <t>188489</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5208,12 +5208,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>100903</t>
+          <t>102160</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>148003</t>
+          <t>150321</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5223,12 +5223,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>244086</t>
+          <t>246333</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>318814</t>
+          <t>318659</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
@@ -5286,12 +5286,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3061433</t>
+          <t>3059276</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>3134957</t>
+          <t>3135347</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5301,12 +5301,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>89,55%</t>
+          <t>89,48%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>91,7%</t>
+          <t>91,71%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5321,12 +5321,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3248223</t>
+          <t>3241762</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3313402</t>
+          <t>3311714</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5336,12 +5336,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>91,39%</t>
+          <t>91,21%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>93,22%</t>
+          <t>93,18%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5356,12 +5356,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>6330561</t>
+          <t>6326154</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>6429371</t>
+          <t>6431564</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5371,12 +5371,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>90,79%</t>
+          <t>90,72%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>92,2%</t>
+          <t>92,23%</t>
         </is>
       </c>
     </row>
@@ -5552,7 +5552,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el Seguro Sanitario del que es beneficiario en 2016</t>
+          <t>Población según el Seguro Sanitario del que es beneficiaria en 2016 (tasa de respuesta: 99,86%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5747,97 +5747,97 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1898</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>0,25%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>2138</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>0,22%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>2029</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -5860,12 +5860,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2854</t>
+          <t>2233</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>13860</t>
+          <t>13283</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5875,12 +5875,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5895,12 +5895,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4434</t>
+          <t>4378</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>19094</t>
+          <t>19238</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5910,12 +5910,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5930,12 +5930,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>9444</t>
+          <t>8894</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>27394</t>
+          <t>26075</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5945,12 +5945,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,5%</t>
         </is>
       </c>
     </row>
@@ -5973,12 +5973,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4217</t>
+          <t>4653</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>17352</t>
+          <t>17204</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6008,12 +6008,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>5205</t>
+          <t>4787</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>18886</t>
+          <t>20219</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6023,12 +6023,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>11291</t>
+          <t>12120</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>29683</t>
+          <t>30899</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6058,12 +6058,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,77%</t>
         </is>
       </c>
     </row>
@@ -6086,12 +6086,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>727996</t>
+          <t>727975</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>744035</t>
+          <t>743997</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6101,12 +6101,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,65%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6121,12 +6121,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>958765</t>
+          <t>958521</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>978353</t>
+          <t>978936</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6136,12 +6136,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>96,75%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6156,12 +6156,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1693941</t>
+          <t>1691735</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1719427</t>
+          <t>1718356</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6171,12 +6171,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>97,01%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,54%</t>
         </is>
       </c>
     </row>
@@ -6316,12 +6316,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1054</t>
+          <t>1057</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>12527</t>
+          <t>13302</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6336,7 +6336,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6351,12 +6351,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>843</t>
+          <t>844</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>8881</t>
+          <t>8320</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6371,7 +6371,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6386,12 +6386,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2614</t>
+          <t>3132</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>15888</t>
+          <t>16489</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,41%</t>
         </is>
       </c>
     </row>
@@ -6429,12 +6429,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>43309</t>
+          <t>42168</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>75154</t>
+          <t>76000</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6444,12 +6444,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>47228</t>
+          <t>46474</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>81636</t>
+          <t>79160</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6479,12 +6479,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6499,12 +6499,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>101572</t>
+          <t>100051</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>147386</t>
+          <t>145688</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6514,12 +6514,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,59%</t>
         </is>
       </c>
     </row>
@@ -6542,12 +6542,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>54927</t>
+          <t>54998</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>89870</t>
+          <t>90018</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6562,7 +6562,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>36393</t>
+          <t>35170</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>64696</t>
+          <t>65372</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6592,12 +6592,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6612,12 +6612,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>98279</t>
+          <t>99432</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>144971</t>
+          <t>145397</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6627,12 +6627,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,58%</t>
         </is>
       </c>
     </row>
@@ -6655,12 +6655,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1915688</t>
+          <t>1915085</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1962269</t>
+          <t>1964104</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6670,12 +6670,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>92,38%</t>
+          <t>92,36%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>94,63%</t>
+          <t>94,72%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6690,12 +6690,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1850290</t>
+          <t>1849878</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1894167</t>
+          <t>1894134</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6705,7 +6705,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>93,15%</t>
+          <t>93,13%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -6725,12 +6725,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>3777102</t>
+          <t>3782206</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>3842997</t>
+          <t>3845020</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6740,12 +6740,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>93,03%</t>
+          <t>93,16%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>94,65%</t>
+          <t>94,7%</t>
         </is>
       </c>
     </row>
@@ -6890,7 +6890,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>8506</t>
+          <t>7677</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6905,7 +6905,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6920,62 +6920,62 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>2438</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>2001</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>8779</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>0,22%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>0,36%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>2438</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>7347</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>0,22%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,8%</t>
         </is>
       </c>
     </row>
@@ -6998,12 +6998,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>43939</t>
+          <t>44206</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>73461</t>
+          <t>73520</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7013,12 +7013,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -7033,12 +7033,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>62163</t>
+          <t>61974</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>98607</t>
+          <t>95547</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7048,12 +7048,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>17,4%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -7068,12 +7068,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>114902</t>
+          <t>113991</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>162440</t>
+          <t>160329</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7083,12 +7083,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>14,64%</t>
         </is>
       </c>
     </row>
@@ -7111,12 +7111,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>61131</t>
+          <t>62295</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>94511</t>
+          <t>96199</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7126,12 +7126,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>11,41%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7146,12 +7146,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>48756</t>
+          <t>47730</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>78322</t>
+          <t>78983</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7161,12 +7161,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7181,12 +7181,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>116531</t>
+          <t>117329</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>161767</t>
+          <t>164335</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7196,12 +7196,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>15,01%</t>
         </is>
       </c>
     </row>
@@ -7224,12 +7224,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>386447</t>
+          <t>388305</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>429394</t>
+          <t>430416</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7239,12 +7239,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>70,79%</t>
+          <t>71,13%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>78,65%</t>
+          <t>78,84%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7259,12 +7259,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>385214</t>
+          <t>386330</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>427648</t>
+          <t>429458</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7274,12 +7274,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>70,15%</t>
+          <t>70,35%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>77,88%</t>
+          <t>78,21%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7294,12 +7294,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>783480</t>
+          <t>785771</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>844789</t>
+          <t>847141</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7309,12 +7309,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>71,55%</t>
+          <t>71,76%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>77,36%</t>
         </is>
       </c>
     </row>
@@ -7454,12 +7454,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2280</t>
+          <t>2276</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>16005</t>
+          <t>15623</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7474,7 +7474,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7489,12 +7489,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>851</t>
+          <t>849</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>8465</t>
+          <t>9300</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7509,7 +7509,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7524,12 +7524,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>4391</t>
+          <t>4538</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>20370</t>
+          <t>18934</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7539,12 +7539,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,07%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,27%</t>
         </is>
       </c>
     </row>
@@ -7567,12 +7567,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>101371</t>
+          <t>100498</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>145633</t>
+          <t>145611</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7582,7 +7582,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -7602,12 +7602,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>128528</t>
+          <t>127438</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>177726</t>
+          <t>178116</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7617,12 +7617,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7637,12 +7637,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>239015</t>
+          <t>237836</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>306028</t>
+          <t>307583</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7652,12 +7652,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,46%</t>
         </is>
       </c>
     </row>
@@ -7680,12 +7680,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>133350</t>
+          <t>131829</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>184669</t>
+          <t>182725</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7695,12 +7695,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7715,12 +7715,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>100808</t>
+          <t>99627</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>145653</t>
+          <t>145079</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7730,12 +7730,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7750,12 +7750,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>247287</t>
+          <t>246347</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>314382</t>
+          <t>313699</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7765,12 +7765,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,55%</t>
         </is>
       </c>
     </row>
@@ -7793,12 +7793,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3052900</t>
+          <t>3053762</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>3118952</t>
+          <t>3122501</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7808,12 +7808,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>90,52%</t>
+          <t>90,54%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>92,48%</t>
+          <t>92,58%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7828,12 +7828,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3216402</t>
+          <t>3216472</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3282418</t>
+          <t>3284402</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7848,7 +7848,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>93,08%</t>
+          <t>93,14%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7863,12 +7863,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>6286636</t>
+          <t>6291059</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>6385098</t>
+          <t>6385821</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7878,12 +7878,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>91,12%</t>
+          <t>91,19%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>92,55%</t>
+          <t>92,56%</t>
         </is>
       </c>
     </row>
@@ -8059,7 +8059,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el Seguro Sanitario del que es beneficiario en 2023</t>
+          <t>Población según el Seguro Sanitario del que es beneficiaria en 2023 (tasa de respuesta: 99,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8259,7 +8259,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5968</t>
+          <t>5819</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8274,7 +8274,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8294,7 +8294,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3561</t>
+          <t>3906</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8309,7 +8309,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8324,12 +8324,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>837</t>
+          <t>808</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7213</t>
+          <t>6573</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8339,12 +8339,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,06%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,52%</t>
         </is>
       </c>
     </row>
@@ -8367,12 +8367,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4787</t>
+          <t>4833</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>16401</t>
+          <t>16226</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8382,12 +8382,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8402,12 +8402,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9216</t>
+          <t>8949</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>21936</t>
+          <t>22433</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8417,12 +8417,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8437,12 +8437,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>16442</t>
+          <t>16325</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>33021</t>
+          <t>32944</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8452,7 +8452,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -8480,12 +8480,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>951</t>
+          <t>952</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7454</t>
+          <t>7784</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8500,7 +8500,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8515,12 +8515,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3104</t>
+          <t>3135</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>11361</t>
+          <t>11471</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8530,47 +8530,47 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
+          <t>0,42%</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>1,52%</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>8985</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>5200</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>14366</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>0,71%</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
           <t>0,41%</t>
         </is>
       </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>1,51%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>8985</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>5151</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>14610</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>0,71%</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>0,41%</t>
-        </is>
-      </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,13%</t>
         </is>
       </c>
     </row>
@@ -8593,12 +8593,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>492466</t>
+          <t>492460</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>506021</t>
+          <t>506391</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8608,12 +8608,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>95,64%</t>
+          <t>95,63%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,34%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8628,12 +8628,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>723330</t>
+          <t>722860</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>738414</t>
+          <t>737564</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>96,04%</t>
+          <t>95,98%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>97,93%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8663,12 +8663,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1222174</t>
+          <t>1221501</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1241697</t>
+          <t>1241268</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8678,12 +8678,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>96,32%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>97,88%</t>
         </is>
       </c>
     </row>
@@ -8828,7 +8828,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6222</t>
+          <t>5092</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8843,7 +8843,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8858,12 +8858,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2221</t>
+          <t>2044</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>10700</t>
+          <t>11178</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8873,12 +8873,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8893,12 +8893,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2472</t>
+          <t>2411</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>12382</t>
+          <t>11283</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8913,7 +8913,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,25%</t>
         </is>
       </c>
     </row>
@@ -8936,12 +8936,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>113732</t>
+          <t>115494</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>199885</t>
+          <t>199288</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8951,12 +8951,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8971,12 +8971,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>116085</t>
+          <t>114741</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>192632</t>
+          <t>192185</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8986,12 +8986,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9006,12 +9006,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>258215</t>
+          <t>261803</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>373997</t>
+          <t>380342</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9021,12 +9021,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,4%</t>
         </is>
       </c>
     </row>
@@ -9049,12 +9049,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>42269</t>
+          <t>44643</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>89453</t>
+          <t>89804</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9064,12 +9064,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9084,12 +9084,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>22915</t>
+          <t>22586</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>47199</t>
+          <t>46078</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9099,12 +9099,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9119,12 +9119,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>75910</t>
+          <t>74387</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>124990</t>
+          <t>124147</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9134,12 +9134,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,74%</t>
         </is>
       </c>
     </row>
@@ -9162,12 +9162,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2014795</t>
+          <t>2016139</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2131230</t>
+          <t>2129942</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>87,97%</t>
+          <t>88,03%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>93,05%</t>
+          <t>93,0%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9197,12 +9197,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1999083</t>
+          <t>2001965</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>2094329</t>
+          <t>2092396</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9212,12 +9212,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>89,34%</t>
+          <t>89,47%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>93,59%</t>
+          <t>93,51%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9232,12 +9232,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>4038005</t>
+          <t>4033955</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>4178324</t>
+          <t>4186130</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9247,12 +9247,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>89,18%</t>
+          <t>89,09%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>92,28%</t>
+          <t>92,45%</t>
         </is>
       </c>
     </row>
@@ -9392,97 +9392,97 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>1821</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>0,28%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
+      <c r="R14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>1262</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>0,19%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>1489</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -9505,12 +9505,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>120532</t>
+          <t>123576</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>166307</t>
+          <t>168602</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9520,12 +9520,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>18,64%</t>
+          <t>19,11%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>26,07%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -9540,12 +9540,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>155023</t>
+          <t>155985</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>194491</t>
+          <t>196821</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9555,12 +9555,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>23,47%</t>
+          <t>23,62%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>29,45%</t>
+          <t>29,8%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -9575,12 +9575,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>290243</t>
+          <t>294767</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>349175</t>
+          <t>352165</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -9590,12 +9590,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>22,21%</t>
+          <t>22,55%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>26,71%</t>
+          <t>26,94%</t>
         </is>
       </c>
     </row>
@@ -9618,12 +9618,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>37093</t>
+          <t>36133</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>62378</t>
+          <t>62076</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9633,12 +9633,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9653,12 +9653,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>46095</t>
+          <t>45420</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>71734</t>
+          <t>69105</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9668,12 +9668,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9688,12 +9688,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>89319</t>
+          <t>87118</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>122644</t>
+          <t>123343</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9703,12 +9703,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,44%</t>
         </is>
       </c>
     </row>
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>430920</t>
+          <t>428945</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>479722</t>
+          <t>478711</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9746,12 +9746,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>66,64%</t>
+          <t>66,34%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>74,19%</t>
+          <t>74,03%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9766,12 +9766,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>407544</t>
+          <t>406690</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>451690</t>
+          <t>449280</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9781,12 +9781,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>61,71%</t>
+          <t>61,58%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>68,39%</t>
+          <t>68,02%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9801,12 +9801,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>850856</t>
+          <t>847951</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>916275</t>
+          <t>911402</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9816,12 +9816,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>65,1%</t>
+          <t>64,87%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>70,1%</t>
+          <t>69,73%</t>
         </is>
       </c>
     </row>
@@ -9961,12 +9961,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>824</t>
+          <t>883</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7392</t>
+          <t>7746</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9976,12 +9976,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,02%</t>
+          <t>0,03%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9996,12 +9996,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2810</t>
+          <t>2963</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>10958</t>
+          <t>11773</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10016,7 +10016,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10031,12 +10031,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>4720</t>
+          <t>4716</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>15424</t>
+          <t>15514</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10074,12 +10074,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>251564</t>
+          <t>249575</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>364550</t>
+          <t>363757</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10089,12 +10089,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10109,12 +10109,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>290612</t>
+          <t>291906</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>392770</t>
+          <t>393617</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10124,12 +10124,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10144,12 +10144,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>586002</t>
+          <t>580402</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>737850</t>
+          <t>736053</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10159,12 +10159,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,36%</t>
         </is>
       </c>
     </row>
@@ -10187,12 +10187,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>88419</t>
+          <t>86955</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>141645</t>
+          <t>142945</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10202,12 +10202,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10222,12 +10222,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>77186</t>
+          <t>77993</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>116491</t>
+          <t>115826</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10237,12 +10237,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10257,12 +10257,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>180382</t>
+          <t>179871</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>246422</t>
+          <t>247606</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,49%</t>
         </is>
       </c>
     </row>
@@ -10300,12 +10300,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2958395</t>
+          <t>2959003</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>3106421</t>
+          <t>3107831</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10315,12 +10315,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>85,7%</t>
+          <t>85,72%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>89,99%</t>
+          <t>90,03%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10335,12 +10335,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3149656</t>
+          <t>3146079</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3281359</t>
+          <t>3271257</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10350,12 +10350,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>86,26%</t>
+          <t>86,16%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>89,87%</t>
+          <t>89,59%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10370,12 +10370,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>6128998</t>
+          <t>6135199</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>6322884</t>
+          <t>6339194</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10385,12 +10385,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>86,29%</t>
+          <t>86,37%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>89,01%</t>
+          <t>89,24%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P22_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P22_R-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1036</t>
+          <t>1033</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13000</t>
+          <t>12542</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5601</t>
+          <t>4647</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1652</t>
+          <t>1645</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12910</t>
+          <t>13703</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,58%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>27740</t>
+          <t>26689</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>53386</t>
+          <t>53118</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>18707</t>
+          <t>18612</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>39476</t>
+          <t>39545</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>49869</t>
+          <t>50299</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>81411</t>
+          <t>83140</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,55%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>9447</t>
+          <t>9542</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>25029</t>
+          <t>25375</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>27243</t>
+          <t>28337</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>51138</t>
+          <t>52805</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>39833</t>
+          <t>40771</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>68815</t>
+          <t>68716</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,93%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>953307</t>
+          <t>953256</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>983447</t>
+          <t>984153</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1092,7 +1092,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>95,65%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1230978</t>
+          <t>1229067</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1262334</t>
+          <t>1262395</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,7 +1122,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>93,66%</t>
+          <t>93,52%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2196378</t>
+          <t>2193612</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>2239163</t>
+          <t>2237883</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>93,74%</t>
+          <t>93,62%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>95,56%</t>
+          <t>95,51%</t>
         </is>
       </c>
     </row>
@@ -1307,7 +1307,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8865</t>
+          <t>11581</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6957</t>
+          <t>4960</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1357,7 +1357,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1377,7 +1377,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>9849</t>
+          <t>9168</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,28%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>83082</t>
+          <t>83731</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>124120</t>
+          <t>123708</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>67111</t>
+          <t>66135</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>102914</t>
+          <t>102388</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>160301</t>
+          <t>163304</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>214492</t>
+          <t>213885</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,53%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>35256</t>
+          <t>35512</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>63939</t>
+          <t>64160</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>45638</t>
+          <t>45693</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>77749</t>
+          <t>77385</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1583,7 +1583,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>89693</t>
+          <t>88467</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>130819</t>
+          <t>130909</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,0%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1511181</t>
+          <t>1513358</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1561041</t>
+          <t>1560700</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>89,43%</t>
+          <t>89,56%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>92,38%</t>
+          <t>92,36%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1413250</t>
+          <t>1415663</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1461658</t>
+          <t>1463284</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>89,08%</t>
+          <t>89,23%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>92,13%</t>
+          <t>92,23%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>2943526</t>
+          <t>2945823</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>3010339</t>
+          <t>3012159</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>89,84%</t>
+          <t>89,91%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>91,88%</t>
+          <t>91,94%</t>
         </is>
       </c>
     </row>
@@ -1984,12 +1984,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>59394</t>
+          <t>59594</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>92359</t>
+          <t>92881</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1999,12 +1999,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>10,81%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>16,84%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2019,12 +2019,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>50717</t>
+          <t>49415</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>81344</t>
+          <t>80684</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2034,12 +2034,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>17,07%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2054,12 +2054,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>118718</t>
+          <t>118190</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>161625</t>
+          <t>161419</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2069,12 +2069,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>15,7%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>51773</t>
+          <t>52500</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>82790</t>
+          <t>82556</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>14,97%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>36149</t>
+          <t>35352</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>62606</t>
+          <t>61614</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>12,93%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>95152</t>
+          <t>95220</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>137153</t>
+          <t>135265</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,7 +2187,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>13,16%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>389801</t>
+          <t>387236</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>432953</t>
+          <t>430075</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>70,69%</t>
+          <t>70,23%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>78,52%</t>
+          <t>78,0%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>342290</t>
+          <t>344002</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>382538</t>
+          <t>383037</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>71,85%</t>
+          <t>72,21%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>80,3%</t>
+          <t>80,4%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>746141</t>
+          <t>747352</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>803096</t>
+          <t>802492</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>72,59%</t>
+          <t>72,71%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>78,14%</t>
+          <t>78,08%</t>
         </is>
       </c>
     </row>
@@ -2440,12 +2440,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1659</t>
+          <t>1656</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>15454</t>
+          <t>15998</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2460,7 +2460,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2480,7 +2480,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6450</t>
+          <t>7014</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2495,7 +2495,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,12 +2510,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3139</t>
+          <t>2864</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>16800</t>
+          <t>17250</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,12 +2525,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,04%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,26%</t>
         </is>
       </c>
     </row>
@@ -2553,12 +2553,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>187060</t>
+          <t>189851</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>246072</t>
+          <t>246640</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2568,12 +2568,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,12 +2588,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>152130</t>
+          <t>152149</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>204233</t>
+          <t>204285</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2603,7 +2603,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2623,12 +2623,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>351145</t>
+          <t>356337</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>431657</t>
+          <t>429891</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,12 +2638,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,47%</t>
         </is>
       </c>
     </row>
@@ -2666,12 +2666,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>109849</t>
+          <t>109043</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>154994</t>
+          <t>152144</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2681,12 +2681,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2701,12 +2701,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>123197</t>
+          <t>123070</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>170664</t>
+          <t>170941</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2716,12 +2716,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2736,12 +2736,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>246468</t>
+          <t>241395</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>314462</t>
+          <t>311429</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2751,12 +2751,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,69%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2883107</t>
+          <t>2877836</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2952586</t>
+          <t>2952131</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>88,16%</t>
+          <t>88,0%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>90,29%</t>
+          <t>90,28%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3017994</t>
+          <t>3018120</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3085285</t>
+          <t>3086836</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>89,36%</t>
+          <t>89,37%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>91,36%</t>
+          <t>91,4%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>5922062</t>
+          <t>5919985</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>6023059</t>
+          <t>6017928</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>89,09%</t>
+          <t>89,06%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>90,61%</t>
+          <t>90,53%</t>
         </is>
       </c>
     </row>
@@ -3245,7 +3245,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7591</t>
+          <t>6846</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3260,7 +3260,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3315,7 +3315,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>10668</t>
+          <t>6940</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3330,7 +3330,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,3%</t>
         </is>
       </c>
     </row>
@@ -3353,12 +3353,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3710</t>
+          <t>3600</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>14402</t>
+          <t>15254</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3368,12 +3368,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3388,12 +3388,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>15432</t>
+          <t>15025</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>36095</t>
+          <t>36575</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3423,12 +3423,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>21688</t>
+          <t>20338</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>44950</t>
+          <t>43150</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,87%</t>
         </is>
       </c>
     </row>
@@ -3466,12 +3466,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7773</t>
+          <t>7698</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>24402</t>
+          <t>22811</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3501,12 +3501,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>12078</t>
+          <t>11956</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>31467</t>
+          <t>30917</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3536,12 +3536,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>23132</t>
+          <t>23761</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>47128</t>
+          <t>48245</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,09%</t>
         </is>
       </c>
     </row>
@@ -3579,12 +3579,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>939562</t>
+          <t>940915</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>960477</t>
+          <t>959804</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3594,12 +3594,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>96,54%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3614,12 +3614,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1277955</t>
+          <t>1279230</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1305993</t>
+          <t>1305855</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3629,12 +3629,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>95,53%</t>
+          <t>95,62%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,61%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3649,12 +3649,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2230037</t>
+          <t>2227822</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>2262121</t>
+          <t>2260309</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3664,12 +3664,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>96,44%</t>
+          <t>96,34%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,75%</t>
         </is>
       </c>
     </row>
@@ -3814,7 +3814,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5255</t>
+          <t>4979</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3829,7 +3829,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3849,7 +3849,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>7182</t>
+          <t>6740</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3864,7 +3864,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3884,7 +3884,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>9692</t>
+          <t>8552</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3899,7 +3899,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,23%</t>
         </is>
       </c>
     </row>
@@ -3922,12 +3922,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>80650</t>
+          <t>82141</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>121228</t>
+          <t>122243</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3937,12 +3937,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3957,12 +3957,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>58537</t>
+          <t>59017</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>93799</t>
+          <t>92974</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3972,12 +3972,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3992,12 +3992,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>146803</t>
+          <t>147987</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>199067</t>
+          <t>201983</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4007,12 +4007,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,43%</t>
         </is>
       </c>
     </row>
@@ -4035,12 +4035,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>61004</t>
+          <t>61900</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>100564</t>
+          <t>100883</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4050,77 +4050,77 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
+          <t>3,15%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>5,14%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>59435</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>44838</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>78679</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>3,38%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>2,55%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>4,48%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>139031</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>115623</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>168479</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>3,74%</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
           <t>3,11%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>5,12%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>59435</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>43471</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>77231</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>3,38%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>2,47%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>4,39%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>139031</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>115281</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>168369</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>3,74%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>3,1%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -4148,12 +4148,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1754882</t>
+          <t>1753063</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1809878</t>
+          <t>1809159</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4163,12 +4163,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>89,4%</t>
+          <t>89,31%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>92,2%</t>
+          <t>92,16%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1597706</t>
+          <t>1598824</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1646903</t>
+          <t>1644839</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4198,12 +4198,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>90,89%</t>
+          <t>90,96%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>93,69%</t>
+          <t>93,57%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>3367619</t>
+          <t>3369492</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>3444697</t>
+          <t>3440589</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4233,12 +4233,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>90,51%</t>
+          <t>90,56%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>92,58%</t>
+          <t>92,47%</t>
         </is>
       </c>
     </row>
@@ -4383,7 +4383,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6936</t>
+          <t>6088</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4398,7 +4398,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4453,7 +4453,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6027</t>
+          <t>4876</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4468,7 +4468,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,52%</t>
         </is>
       </c>
     </row>
@@ -4491,12 +4491,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>36008</t>
+          <t>37531</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>66005</t>
+          <t>66363</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>13,79%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>39271</t>
+          <t>38781</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>68570</t>
+          <t>66386</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4541,12 +4541,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>83416</t>
+          <t>81932</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>123926</t>
+          <t>121273</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -4576,12 +4576,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>12,9%</t>
         </is>
       </c>
     </row>
@@ -4604,12 +4604,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>50331</t>
+          <t>50322</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>84502</t>
+          <t>85774</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4624,7 +4624,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>17,56%</t>
+          <t>17,83%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4639,12 +4639,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>30979</t>
+          <t>31128</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>58950</t>
+          <t>59142</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4654,12 +4654,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4674,12 +4674,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>87422</t>
+          <t>87276</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>133585</t>
+          <t>131220</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4689,12 +4689,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>13,96%</t>
         </is>
       </c>
     </row>
@@ -4717,12 +4717,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>341271</t>
+          <t>341821</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>383030</t>
+          <t>383527</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4732,12 +4732,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>70,92%</t>
+          <t>71,04%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>79,6%</t>
+          <t>79,71%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4752,12 +4752,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>344303</t>
+          <t>345379</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>382827</t>
+          <t>382235</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4767,12 +4767,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>75,07%</t>
+          <t>75,31%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>83,47%</t>
+          <t>83,34%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4787,12 +4787,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>699010</t>
+          <t>701013</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>756274</t>
+          <t>757677</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4802,12 +4802,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>74,38%</t>
+          <t>74,59%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>80,47%</t>
+          <t>80,62%</t>
         </is>
       </c>
     </row>
@@ -4947,12 +4947,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1211</t>
+          <t>1204</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9940</t>
+          <t>9947</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -4987,7 +4987,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5999</t>
+          <t>5186</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5002,7 +5002,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5017,12 +5017,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1266</t>
+          <t>1232</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>12300</t>
+          <t>12613</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5060,12 +5060,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>133121</t>
+          <t>132695</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>184560</t>
+          <t>186620</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5075,12 +5075,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5095,12 +5095,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>128005</t>
+          <t>125849</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>177270</t>
+          <t>177360</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5110,7 +5110,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -5130,12 +5130,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>270528</t>
+          <t>272752</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>344047</t>
+          <t>343716</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5145,7 +5145,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -5173,12 +5173,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>130686</t>
+          <t>133051</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>188489</t>
+          <t>187838</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5208,12 +5208,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>102160</t>
+          <t>102777</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>150321</t>
+          <t>147231</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5223,12 +5223,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>246333</t>
+          <t>246532</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>318659</t>
+          <t>317877</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5258,12 +5258,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,56%</t>
         </is>
       </c>
     </row>
@@ -5286,12 +5286,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3059276</t>
+          <t>3061400</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>3135347</t>
+          <t>3135856</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5301,12 +5301,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>89,48%</t>
+          <t>89,55%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>91,71%</t>
+          <t>91,72%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5321,12 +5321,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3241762</t>
+          <t>3245390</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3311714</t>
+          <t>3312954</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5336,12 +5336,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>91,21%</t>
+          <t>91,31%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>93,18%</t>
+          <t>93,21%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5356,12 +5356,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>6326154</t>
+          <t>6328543</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>6431564</t>
+          <t>6428850</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5371,12 +5371,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>90,72%</t>
+          <t>90,76%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>92,23%</t>
+          <t>92,2%</t>
         </is>
       </c>
     </row>
@@ -5860,12 +5860,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2233</t>
+          <t>3039</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>13283</t>
+          <t>13928</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5875,12 +5875,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5895,12 +5895,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4378</t>
+          <t>4487</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>19238</t>
+          <t>19058</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5910,12 +5910,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5930,12 +5930,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>8894</t>
+          <t>9559</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>26075</t>
+          <t>28095</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5945,12 +5945,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,61%</t>
         </is>
       </c>
     </row>
@@ -5973,12 +5973,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4653</t>
+          <t>3953</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>17204</t>
+          <t>16419</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6008,12 +6008,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4787</t>
+          <t>4939</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>20219</t>
+          <t>18520</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6023,12 +6023,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>12120</t>
+          <t>11240</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>30899</t>
+          <t>29903</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6058,12 +6058,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,71%</t>
         </is>
       </c>
     </row>
@@ -6086,12 +6086,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>727975</t>
+          <t>728340</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>743997</t>
+          <t>744452</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6101,12 +6101,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>96,7%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,84%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6121,12 +6121,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>958521</t>
+          <t>959063</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>978936</t>
+          <t>978940</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6136,7 +6136,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>96,81%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -6156,12 +6156,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1691735</t>
+          <t>1692810</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1718356</t>
+          <t>1717723</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6171,12 +6171,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>97,07%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,5%</t>
         </is>
       </c>
     </row>
@@ -6316,12 +6316,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1057</t>
+          <t>1056</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>13302</t>
+          <t>15665</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6336,7 +6336,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6351,12 +6351,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>844</t>
+          <t>851</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>8320</t>
+          <t>8908</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6371,42 +6371,42 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
+          <t>0,45%</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>7474</t>
+        </is>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>2909</t>
+        </is>
+      </c>
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>16948</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
+          <t>0,18%</t>
+        </is>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>0,07%</t>
+        </is>
+      </c>
+      <c r="W9" s="2" t="inlineStr">
+        <is>
           <t>0,42%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>7474</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>3132</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>16489</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>0,18%</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>0,08%</t>
-        </is>
-      </c>
-      <c r="W9" s="2" t="inlineStr">
-        <is>
-          <t>0,41%</t>
         </is>
       </c>
     </row>
@@ -6429,12 +6429,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>42168</t>
+          <t>43749</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>76000</t>
+          <t>74475</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6444,12 +6444,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>46474</t>
+          <t>46979</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>79160</t>
+          <t>80414</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6479,12 +6479,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6499,12 +6499,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>100051</t>
+          <t>99391</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>145688</t>
+          <t>145603</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6514,7 +6514,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>54998</t>
+          <t>53927</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>90018</t>
+          <t>89501</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6557,12 +6557,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>35170</t>
+          <t>35592</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>65372</t>
+          <t>64385</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6592,12 +6592,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6612,12 +6612,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>99432</t>
+          <t>98281</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>145397</t>
+          <t>141282</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6627,12 +6627,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,48%</t>
         </is>
       </c>
     </row>
@@ -6655,12 +6655,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1915085</t>
+          <t>1916871</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1964104</t>
+          <t>1963510</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6670,12 +6670,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>92,36%</t>
+          <t>92,44%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>94,72%</t>
+          <t>94,69%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6690,12 +6690,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1849878</t>
+          <t>1850035</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1894134</t>
+          <t>1892090</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6710,7 +6710,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>95,25%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6725,12 +6725,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>3782206</t>
+          <t>3782380</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>3845020</t>
+          <t>3843462</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6745,7 +6745,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>94,7%</t>
+          <t>94,67%</t>
         </is>
       </c>
     </row>
@@ -6890,7 +6890,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>7677</t>
+          <t>8592</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6905,7 +6905,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6960,7 +6960,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>8779</t>
+          <t>7424</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6975,7 +6975,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,68%</t>
         </is>
       </c>
     </row>
@@ -6998,12 +6998,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>44206</t>
+          <t>44368</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>73520</t>
+          <t>72276</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7013,12 +7013,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -7033,12 +7033,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>61974</t>
+          <t>63721</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>95547</t>
+          <t>96835</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7048,12 +7048,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>17,63%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -7068,12 +7068,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>113991</t>
+          <t>115005</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>160329</t>
+          <t>163547</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7083,12 +7083,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>14,93%</t>
         </is>
       </c>
     </row>
@@ -7111,12 +7111,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>62295</t>
+          <t>60862</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>96199</t>
+          <t>95585</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7126,12 +7126,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>17,51%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7146,12 +7146,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>47730</t>
+          <t>47940</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>78983</t>
+          <t>77944</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7161,12 +7161,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>14,19%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7181,12 +7181,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>117329</t>
+          <t>116990</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>164335</t>
+          <t>162171</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7196,12 +7196,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>14,81%</t>
         </is>
       </c>
     </row>
@@ -7224,12 +7224,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>388305</t>
+          <t>387293</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>430416</t>
+          <t>428407</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7239,12 +7239,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>71,13%</t>
+          <t>70,94%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>78,84%</t>
+          <t>78,47%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7259,12 +7259,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>386330</t>
+          <t>384688</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>429458</t>
+          <t>427366</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7274,12 +7274,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>70,35%</t>
+          <t>70,05%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>78,21%</t>
+          <t>77,82%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7294,12 +7294,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>785771</t>
+          <t>787292</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>847141</t>
+          <t>845770</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7309,12 +7309,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>71,76%</t>
+          <t>71,89%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>77,36%</t>
+          <t>77,23%</t>
         </is>
       </c>
     </row>
@@ -7454,12 +7454,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2276</t>
+          <t>2446</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>15623</t>
+          <t>16165</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7474,7 +7474,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7489,12 +7489,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>849</t>
+          <t>846</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>9300</t>
+          <t>8731</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7509,7 +7509,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7524,12 +7524,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>4538</t>
+          <t>4221</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>18934</t>
+          <t>19012</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7539,12 +7539,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,06%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,28%</t>
         </is>
       </c>
     </row>
@@ -7567,12 +7567,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>100498</t>
+          <t>98385</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>145611</t>
+          <t>143462</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7582,12 +7582,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7602,12 +7602,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>127438</t>
+          <t>125060</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>178116</t>
+          <t>178635</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7617,12 +7617,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7637,12 +7637,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>237836</t>
+          <t>238151</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>307583</t>
+          <t>304008</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7657,7 +7657,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,41%</t>
         </is>
       </c>
     </row>
@@ -7680,12 +7680,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>131829</t>
+          <t>133595</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>182725</t>
+          <t>185422</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7695,12 +7695,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7715,12 +7715,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>99627</t>
+          <t>99804</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>145079</t>
+          <t>146181</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7735,7 +7735,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7750,12 +7750,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>246347</t>
+          <t>248169</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>313699</t>
+          <t>316402</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7765,12 +7765,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,59%</t>
         </is>
       </c>
     </row>
@@ -7793,12 +7793,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3053762</t>
+          <t>3051357</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>3122501</t>
+          <t>3120306</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7808,12 +7808,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>90,54%</t>
+          <t>90,47%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>92,58%</t>
+          <t>92,52%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7828,12 +7828,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3216472</t>
+          <t>3215534</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3284402</t>
+          <t>3282379</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7843,12 +7843,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>91,21%</t>
+          <t>91,19%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>93,14%</t>
+          <t>93,08%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7863,12 +7863,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>6291059</t>
+          <t>6297519</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>6385821</t>
+          <t>6384414</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7878,12 +7878,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>91,19%</t>
+          <t>91,28%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>92,56%</t>
+          <t>92,54%</t>
         </is>
       </c>
     </row>
@@ -8249,7 +8249,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>1691</t>
+          <t>1952</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5819</t>
+          <t>7628</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -8274,7 +8274,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8284,7 +8284,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1140</t>
+          <t>1304</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -8294,12 +8294,12 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3906</t>
+          <t>4645</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -8309,7 +8309,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8319,32 +8319,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>2831</t>
+          <t>3256</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>808</t>
+          <t>914</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6573</t>
+          <t>8106</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,07%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,58%</t>
         </is>
       </c>
     </row>
@@ -8362,32 +8362,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>9473</t>
+          <t>9663</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4833</t>
+          <t>5633</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>16226</t>
+          <t>17487</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8397,32 +8397,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>14107</t>
+          <t>14763</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8949</t>
+          <t>9531</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>22433</t>
+          <t>22449</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8432,32 +8432,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>23580</t>
+          <t>24427</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>16325</t>
+          <t>16582</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>32944</t>
+          <t>33652</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,4%</t>
         </is>
       </c>
     </row>
@@ -8475,17 +8475,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2928</t>
+          <t>3299</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>952</t>
+          <t>987</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7784</t>
+          <t>8423</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8495,12 +8495,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8510,22 +8510,22 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>6057</t>
+          <t>6460</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3135</t>
+          <t>3462</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>11471</t>
+          <t>12686</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
@@ -8535,7 +8535,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8545,32 +8545,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>8985</t>
+          <t>9759</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>5200</t>
+          <t>5373</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>14366</t>
+          <t>16006</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,14%</t>
         </is>
       </c>
     </row>
@@ -8588,67 +8588,67 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>500847</t>
+          <t>563614</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>492460</t>
+          <t>554884</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>506391</t>
+          <t>569751</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
+          <t>97,42%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>95,91%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>98,48%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>1389</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>798787</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>789616</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>805318</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
           <t>97,26%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>95,63%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>98,34%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>1389</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>731863</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>722860</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>737564</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>97,17%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>96,14%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8658,32 +8658,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>1232711</t>
+          <t>1362403</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1221501</t>
+          <t>1350947</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1241268</t>
+          <t>1372624</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>97,33%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>96,51%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>98,06%</t>
         </is>
       </c>
     </row>
@@ -8701,17 +8701,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8736,17 +8736,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>753168</t>
+          <t>821315</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>753168</t>
+          <t>821315</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>753168</t>
+          <t>821315</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8771,17 +8771,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1268107</t>
+          <t>1399845</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1268107</t>
+          <t>1399845</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1268107</t>
+          <t>1399845</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8818,7 +8818,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1177</t>
+          <t>2966</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -8828,12 +8828,12 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5092</t>
+          <t>10776</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -8843,7 +8843,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8853,67 +8853,67 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4854</t>
+          <t>5355</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2044</t>
+          <t>2289</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>11178</t>
+          <t>10806</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
+          <t>0,11%</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>0,5%</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>8321</t>
+        </is>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>4099</t>
+        </is>
+      </c>
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>16899</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
+          <t>0,19%</t>
+        </is>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
           <t>0,09%</t>
         </is>
       </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>0,5%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>6032</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>2411</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>11283</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>0,13%</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>0,05%</t>
-        </is>
-      </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,38%</t>
         </is>
       </c>
     </row>
@@ -8931,32 +8931,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>163009</t>
+          <t>172325</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>115494</t>
+          <t>145653</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>199288</t>
+          <t>204407</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8966,67 +8966,67 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>161603</t>
+          <t>180269</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>114741</t>
+          <t>158639</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>192185</t>
+          <t>204428</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
+          <t>8,31%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>7,31%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>9,42%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>397</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>352594</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>317894</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>391455</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>8,01%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
           <t>7,22%</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>5,13%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>8,59%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>397</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>324612</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>261803</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>380342</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>7,17%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>5,78%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,89%</t>
         </is>
       </c>
     </row>
@@ -9044,32 +9044,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>65622</t>
+          <t>70918</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>44643</t>
+          <t>53423</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>89804</t>
+          <t>92589</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9079,32 +9079,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>33807</t>
+          <t>36427</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>22586</t>
+          <t>28134</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>46078</t>
+          <t>48300</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9114,32 +9114,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>99430</t>
+          <t>107345</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>74387</t>
+          <t>88043</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>124147</t>
+          <t>132491</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>3,01%</t>
         </is>
       </c>
     </row>
@@ -9157,32 +9157,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2060518</t>
+          <t>1984357</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2016139</t>
+          <t>1950555</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2129942</t>
+          <t>2018373</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>89,97%</t>
+          <t>88,96%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>88,03%</t>
+          <t>87,45%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>93,0%</t>
+          <t>90,49%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9192,32 +9192,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2037396</t>
+          <t>1948275</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2001965</t>
+          <t>1921002</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>2092396</t>
+          <t>1972909</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>91,05%</t>
+          <t>89,77%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>89,47%</t>
+          <t>88,51%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>93,51%</t>
+          <t>90,9%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9227,32 +9227,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>4097914</t>
+          <t>3932632</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>4033955</t>
+          <t>3888386</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>4186130</t>
+          <t>3969824</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>90,5%</t>
+          <t>89,36%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>89,09%</t>
+          <t>88,35%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>92,45%</t>
+          <t>90,2%</t>
         </is>
       </c>
     </row>
@@ -9270,17 +9270,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9305,17 +9305,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2237661</t>
+          <t>2170326</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2237661</t>
+          <t>2170326</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2237661</t>
+          <t>2170326</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9340,17 +9340,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>4527988</t>
+          <t>4400892</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4527988</t>
+          <t>4400892</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4527988</t>
+          <t>4400892</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9500,32 +9500,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>145454</t>
+          <t>162589</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>123576</t>
+          <t>139049</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>168602</t>
+          <t>189105</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>22,49%</t>
+          <t>22,85%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>19,54%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>26,07%</t>
+          <t>26,58%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -9535,32 +9535,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>175329</t>
+          <t>193533</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>155985</t>
+          <t>173463</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>196821</t>
+          <t>214314</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>26,55%</t>
+          <t>26,34%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>23,62%</t>
+          <t>23,6%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>29,8%</t>
+          <t>29,16%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -9570,32 +9570,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>320783</t>
+          <t>356122</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>294767</t>
+          <t>325924</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>352165</t>
+          <t>391341</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>24,54%</t>
+          <t>24,62%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>22,55%</t>
+          <t>22,53%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>26,94%</t>
+          <t>27,06%</t>
         </is>
       </c>
     </row>
@@ -9613,32 +9613,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>47533</t>
+          <t>55434</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>36133</t>
+          <t>42207</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>62076</t>
+          <t>70996</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9648,32 +9648,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>56557</t>
+          <t>59767</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>45420</t>
+          <t>48153</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>69105</t>
+          <t>74176</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9683,17 +9683,17 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>104090</t>
+          <t>115200</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>87118</t>
+          <t>97479</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>123343</t>
+          <t>135173</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9703,12 +9703,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,35%</t>
         </is>
       </c>
     </row>
@@ -9726,32 +9726,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>453636</t>
+          <t>493564</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>428945</t>
+          <t>463476</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>478711</t>
+          <t>517467</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>70,15%</t>
+          <t>69,36%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>66,34%</t>
+          <t>65,13%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>74,03%</t>
+          <t>72,72%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9761,32 +9761,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>428576</t>
+          <t>481577</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>406690</t>
+          <t>458765</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>449280</t>
+          <t>503298</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>64,89%</t>
+          <t>65,53%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>61,58%</t>
+          <t>62,43%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>68,02%</t>
+          <t>68,49%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9796,32 +9796,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>882213</t>
+          <t>975141</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>847951</t>
+          <t>938430</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>911402</t>
+          <t>1006863</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>67,49%</t>
+          <t>67,42%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>64,87%</t>
+          <t>64,88%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>69,73%</t>
+          <t>69,61%</t>
         </is>
       </c>
     </row>
@@ -9839,17 +9839,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9874,17 +9874,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9909,17 +9909,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9956,22 +9956,22 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2868</t>
+          <t>4917</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>883</t>
+          <t>1147</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7746</t>
+          <t>12570</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -9981,7 +9981,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9991,67 +9991,67 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>5995</t>
+          <t>6660</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2963</t>
+          <t>2792</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>11773</t>
+          <t>11977</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
+          <t>0,18%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>0,07%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>0,32%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>11577</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>6424</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>19729</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
           <t>0,16%</t>
         </is>
       </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>0,08%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>0,32%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>8863</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>4716</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>15514</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>0,12%</t>
-        </is>
-      </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,27%</t>
         </is>
       </c>
     </row>
@@ -10069,32 +10069,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>317936</t>
+          <t>344578</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>249575</t>
+          <t>306969</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>363757</t>
+          <t>388366</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10104,32 +10104,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>351040</t>
+          <t>388565</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>291906</t>
+          <t>353434</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>393617</t>
+          <t>423699</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10139,32 +10139,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>668975</t>
+          <t>733143</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>580402</t>
+          <t>681330</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>736053</t>
+          <t>783363</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,81%</t>
         </is>
       </c>
     </row>
@@ -10182,32 +10182,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>116083</t>
+          <t>129651</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>86955</t>
+          <t>107341</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>142945</t>
+          <t>156346</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10217,32 +10217,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>96422</t>
+          <t>102653</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>77993</t>
+          <t>87374</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>115826</t>
+          <t>119813</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10252,32 +10252,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>212505</t>
+          <t>232305</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>179871</t>
+          <t>205686</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>247606</t>
+          <t>263777</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,64%</t>
         </is>
       </c>
     </row>
@@ -10295,32 +10295,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>3015002</t>
+          <t>3041537</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2959003</t>
+          <t>2991853</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>3107831</t>
+          <t>3086921</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>87,34%</t>
+          <t>86,39%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>85,72%</t>
+          <t>84,98%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>90,03%</t>
+          <t>87,68%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10330,32 +10330,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>3197836</t>
+          <t>3228641</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3146079</t>
+          <t>3191463</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3271257</t>
+          <t>3267913</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>87,58%</t>
+          <t>86,64%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>86,16%</t>
+          <t>85,64%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>89,59%</t>
+          <t>87,69%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10365,32 +10365,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>6212838</t>
+          <t>6270176</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>6135199</t>
+          <t>6209844</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>6339194</t>
+          <t>6326080</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>87,47%</t>
+          <t>86,52%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>86,37%</t>
+          <t>85,69%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>89,24%</t>
+          <t>87,29%</t>
         </is>
       </c>
     </row>
@@ -10408,17 +10408,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10443,17 +10443,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>3651292</t>
+          <t>3726519</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3651292</t>
+          <t>3726519</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3651292</t>
+          <t>3726519</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10478,17 +10478,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>7103181</t>
+          <t>7247201</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>7103181</t>
+          <t>7247201</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>7103181</t>
+          <t>7247201</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
